--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEW_JERSEY_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEW_JERSEY_2021.xlsx
@@ -1219,7 +1219,7 @@
         <v>18</v>
       </c>
       <c r="D48">
-        <v>0.0009187892399571231</v>
+        <v>0.0009187892399571232</v>
       </c>
     </row>
     <row r="49">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C214">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C222">
@@ -5773,7 +5773,7 @@
         <v>18</v>
       </c>
       <c r="D301">
-        <v>0.0009187892399571231</v>
+        <v>0.0009187892399571232</v>
       </c>
     </row>
     <row r="302">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C684">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C685">
@@ -13585,7 +13585,7 @@
         <v>18</v>
       </c>
       <c r="D735">
-        <v>0.0009187892399571231</v>
+        <v>0.0009187892399571232</v>
       </c>
     </row>
     <row r="736">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C765">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C766">
@@ -15637,7 +15637,7 @@
         <v>192</v>
       </c>
       <c r="D849">
-        <v>0.009800418559542647</v>
+        <v>0.009800418559542648</v>
       </c>
     </row>
     <row r="850">
@@ -18157,7 +18157,7 @@
         <v>18</v>
       </c>
       <c r="D989">
-        <v>0.0009187892399571231</v>
+        <v>0.0009187892399571232</v>
       </c>
     </row>
     <row r="990">
@@ -20335,7 +20335,7 @@
         <v>18</v>
       </c>
       <c r="D1110">
-        <v>0.0009187892399571231</v>
+        <v>0.0009187892399571232</v>
       </c>
     </row>
     <row r="1111">
@@ -22207,7 +22207,7 @@
         <v>18</v>
       </c>
       <c r="D1214">
-        <v>0.0009187892399571231</v>
+        <v>0.0009187892399571232</v>
       </c>
     </row>
     <row r="1215">
@@ -22549,7 +22549,7 @@
         <v>18</v>
       </c>
       <c r="D1233">
-        <v>0.0009187892399571231</v>
+        <v>0.0009187892399571232</v>
       </c>
     </row>
     <row r="1234">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1247">
@@ -22909,7 +22909,7 @@
         <v>18</v>
       </c>
       <c r="D1253">
-        <v>0.0009187892399571231</v>
+        <v>0.0009187892399571232</v>
       </c>
     </row>
     <row r="1254">
